--- a/kits/security-questionnaire/samples/questionnaire/cobalt-ridge-supplier-security-questionnaire.xlsx
+++ b/kits/security-questionnaire/samples/questionnaire/cobalt-ridge-supplier-security-questionnaire.xlsx
@@ -23,16 +23,16 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="16"/>
       <color rgb="00203864"/>
-      <sz val="16"/>
     </font>
     <font>
       <i val="1"/>
@@ -43,8 +43,8 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
       <color rgb="00203864"/>
-      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -610,8 +610,8 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
@@ -639,7 +639,7 @@
       </c>
       <c r="C3" s="7" t="n"/>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
